--- a/IPPU/A1_Outputs/A-O_AR_Projections_COMPLETED.xlsx
+++ b/IPPU/A1_Outputs/A-O_AR_Projections_COMPLETED.xlsx
@@ -7024,13 +7024,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D2E7272-4660-44E0-9FA3-D48DB948133C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D1C1C44-D21E-475C-93A2-69D498B72BDF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83083D58-F905-42EB-88C5-F64FD8EA1CD3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03A0A9EF-E881-48F1-9443-C855794C38CB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3064D07F-3858-474A-A9B5-01E3A469DC87}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC0D5C8F-107D-421B-A4EC-694C809F6440}"/>
 </file>